--- a/SmartAutoVision/Config/NewKeys.xlsx
+++ b/SmartAutoVision/Config/NewKeys.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="274">
   <si>
     <t xml:space="preserve">Key</t>
   </si>
@@ -801,6 +801,39 @@
   </si>
   <si>
     <t xml:space="preserve">图像[自动采集相机标定点]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{0}事件触发:{1}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OnSubscribeProcessEvent,F:\项目\Libraries\Class\Common\StartMode\StarterTrig.cs,49 line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">自动采集相机标定点+极柱</t>
+  </si>
+  <si>
+    <t xml:space="preserve">自动采集相机标定点+极柱_copy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">自动采集相机标定点-极柱</t>
+  </si>
+  <si>
+    <t xml:space="preserve">采集完成-写最终结果</t>
+  </si>
+  <si>
+    <t xml:space="preserve">延时1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">模拟人工定位用时</t>
+  </si>
+  <si>
+    <t xml:space="preserve">图像[自动采集相机标定点+极柱]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">图像[自动采集相机标定点-极柱]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">任务7</t>
   </si>
 </sst>
 </file>
@@ -2897,6 +2930,116 @@
         <v>86</v>
       </c>
     </row>
+    <row r="187">
+      <c r="A187" t="s">
+        <v>263</v>
+      </c>
+      <c r="B187" t="s">
+        <v>85</v>
+      </c>
+      <c r="C187" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="s">
+        <v>265</v>
+      </c>
+      <c r="B188" t="s">
+        <v>7</v>
+      </c>
+      <c r="C188" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s">
+        <v>266</v>
+      </c>
+      <c r="B189" t="s">
+        <v>7</v>
+      </c>
+      <c r="C189" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s">
+        <v>267</v>
+      </c>
+      <c r="B190" t="s">
+        <v>7</v>
+      </c>
+      <c r="C190" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s">
+        <v>268</v>
+      </c>
+      <c r="B191" t="s">
+        <v>16</v>
+      </c>
+      <c r="C191" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s">
+        <v>269</v>
+      </c>
+      <c r="B192" t="s">
+        <v>250</v>
+      </c>
+      <c r="C192" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="s">
+        <v>270</v>
+      </c>
+      <c r="B193" t="s">
+        <v>250</v>
+      </c>
+      <c r="C193" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="s">
+        <v>271</v>
+      </c>
+      <c r="B194" t="s">
+        <v>85</v>
+      </c>
+      <c r="C194" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="s">
+        <v>272</v>
+      </c>
+      <c r="B195" t="s">
+        <v>85</v>
+      </c>
+      <c r="C195" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="s">
+        <v>273</v>
+      </c>
+      <c r="B196" t="s">
+        <v>7</v>
+      </c>
+      <c r="C196" t="s">
+        <v>99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
